--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases Details" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Cases Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>10.236s</t>
+          <t>10.221s</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>11.004</v>
+        <v>10.954</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.228</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.24</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.204</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.217</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.221</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.261</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.218</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.215</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.227</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.196</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.199</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.208</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.215</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.237</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.213</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.201</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.214</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.218</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.24</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.244</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.231</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.266</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.234</v>
+        <v>10.249</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.248</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.218</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.241</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.203</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.206</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.428</v>
+        <v>10.447</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.205</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.23</v>
+        <v>10.243</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.221</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.243</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.228</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.237</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.225</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.193</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.197</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.207</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.231</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.214</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.198</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.222</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>10.199</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>10.215</v>
+        <v>10.217</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10.227</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.246</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.239</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.208</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.39</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.205</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.226</v>
+        <v>10.217</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.246</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.203</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.227</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.238</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.219</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>10.36</v>
+        <v>11.222</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.212</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.235</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.243</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.204</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.255</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.221</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10.252</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.216</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.245</v>
+        <v>10.222</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>10.214</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.216</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.209</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.203</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.203</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.235</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.197</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10.188</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.202</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>10.191</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.218</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.286</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.228</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.218</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.198</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.199</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>10.215</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.219</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.204</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>10.355</v>
+        <v>10.348</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>10.219</v>
+        <v>10.229</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.213</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>10.344</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.235</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.224</v>
+        <v>10.217</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>10.228</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.239</v>
+        <v>10.222</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>10.235</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>10.215</v>
+        <v>10.217</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.185</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>10.215</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>10.216</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>10.211</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10.228</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>10.224</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10.221</v>
+        <v>10.213</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.231</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>10.201</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10.239</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>10.21</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>10.333</v>
+        <v>10.314</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>10.205</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.259</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>10.197</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>10.201</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10.212</v>
+        <v>10.238</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>10.238</v>
+        <v>10.213</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>10.246</v>
+        <v>10.222</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>10.343</v>
+        <v>10.333</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.239</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>10.24</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>10.332</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>10.216</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>10.233</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10.239</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>10.213</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>10.183</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>10.201</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>10.209</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>10.195</v>
+        <v>10.248</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>10.202</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>10.195</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>10.264</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>10.239</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>10.198</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>10.191</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.2</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>10.232</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>10.274</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>10.193</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>10.231</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>10.22</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>10.245</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>10.228</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>10.255</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>10.335</v>
+        <v>10.348</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>10.196</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>10.203</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>10.255</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>10.292</v>
+        <v>10.328</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>10.365</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>10.253</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>10.239</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>10.255</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>10.19</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>10.268</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>10.228</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>10.193</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>10.207</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>10.205</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>10.211</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>10.198</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>10.191</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>10.25</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>10.262</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>10.252</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>10.257</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>10.24</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>10.224</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>10.233</v>
+        <v>10.213</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>10.21</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>10.209</v>
+        <v>10.229</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>10.252</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>10.305</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>10.236</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>10.252</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>10.236</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>10.209</v>
+        <v>10.248</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>10.318</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>10.212</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>10.187</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>10.242</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>10.253</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>10.19</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>10.242</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>10.207</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>10.23</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>10.243</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>10.227</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>10.246</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>10.208</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>10.248</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>10.246</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>10.247</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>10.24</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>10.303</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>10.184</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>10.244</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>10.267</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>10.186</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>10.219</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>10.224</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>10.368</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>10.258</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>10.256</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>10.229</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>10.221</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>10.314</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>10.207</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>10.193</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>10.215</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>10.229</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>10.225</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>10.215</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.214</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>10.206</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>10.229</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>10.195</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>10.22</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>10.219</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>10.232</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="F224" s="4" t="n">
-        <v>10.228</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>10.244</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>10.24</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>10.262</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>10.222</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>10.259</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>10.213</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>10.241</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="F232" s="4" t="n">
-        <v>10.235</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>10.243</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>10.334</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>10.242</v>
+        <v>10.072</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>10.249</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>10.245</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>10.225</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>10.303</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>10.241</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>10.236</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>10.204</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>10.242</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>10.234</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>10.218</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F246" s="4" t="n">
-        <v>10.223</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>10.227</v>
+        <v>10.229</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>10.23</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>10.251</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>10.219</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>10.218</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>10.229</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>10.204</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>10.23</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>10.239</v>
+        <v>10.064</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>10.279</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>10.209</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>10.237</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>10.215</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>10.258</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F262" s="4" t="n">
-        <v>10.205</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>10.343</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>10.235</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>10.214</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="F266" s="4" t="n">
-        <v>10.247</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>10.227</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>10.318</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>10.243</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>10.201</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>10.239</v>
+        <v>10.231</v>
       </c>
     </row>
   </sheetData>

--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>10.221s</t>
+          <t>10.236s</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>10.954</v>
+        <v>10.779</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.198</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.181</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.214</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.187</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.192</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.179</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.184</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.262</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.2</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.191</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.2</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.175</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.191</v>
+        <v>10.263</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.204</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.172</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.206</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.21</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.189</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.201</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.191</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.195</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.187</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.249</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.209</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.226</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.216</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.177</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.447</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.189</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.243</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.247</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.187</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.162</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.22</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.221</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.181</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.219</v>
+        <v>10.273</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.187</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.198</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.187</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.195</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>10.186</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>10.217</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10.199</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.179</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.171</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.219</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.341</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.199</v>
+        <v>10.217</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.217</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.189</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.2</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.177</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.175</v>
+        <v>10.249</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.202</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>11.222</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.18</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.183</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.197</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.225</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.214</v>
+        <v>10.245</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.193</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10.171</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.174</v>
+        <v>10.308</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.222</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>10.179</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.226</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.231</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.172</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.233</v>
+        <v>10.245</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.17</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10.187</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.193</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>10.164</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.178</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.31</v>
+        <v>10.222</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.221</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.199</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.189</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.216</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>10.227</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.182</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.198</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>10.348</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>10.229</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.233</v>
+        <v>10.234</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>10.236</v>
+        <v>10.238</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.21</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.217</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>10.214</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.222</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>10.219</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>10.217</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.207</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>10.231</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>10.211</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>10.22</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10.202</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>10.21</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10.213</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.199</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>10.203</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10.22</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>10.216</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>10.314</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>10.193</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.227</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>10.204</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>10.23</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10.238</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>10.213</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>10.222</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>10.333</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>10.232</v>
+        <v>10.354</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.224</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>10.219</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>10.325</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>10.237</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>10.255</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10.216</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>10.228</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>10.219</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>10.177</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>10.218</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>10.248</v>
+        <v>10.313</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>10.22</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>10.228</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>10.227</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>10.21</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>10.224</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.209</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>10.187</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>10.219</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>10.188</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>10.223</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>10.188</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>10.221</v>
+        <v>10.238</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>10.199</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>10.21</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>10.348</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>10.207</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>10.21</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>10.218</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>10.328</v>
+        <v>10.249</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>10.306</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>10.211</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>10.233</v>
+        <v>10.366</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>10.207</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>10.212</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>10.206</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>10.202</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>10.185</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>10.188</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>10.221</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>10.216</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>10.221</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>10.228</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>10.219</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>10.211</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>10.209</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>10.231</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>10.226</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>10.216</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>10.213</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>10.224</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>10.239</v>
+        <v>10.259</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>10.229</v>
+        <v>10.213</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>10.209</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>10.301</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>10.199</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>10.206</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>10.198</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>10.248</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>10.3</v>
+        <v>10.248</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>10.196</v>
+        <v>10.087</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>10.212</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>10.179</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>10.188</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>10.227</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>10.2</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>10.195</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>10.214</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>10.207</v>
+        <v>10.225</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>10.19</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>10.22</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>10.193</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>10.187</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>10.193</v>
+        <v>10.229</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>10.203</v>
+        <v>10.249</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>10.196</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>10.178</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>10.21</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>10.2</v>
+        <v>10.238</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>10.2</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>10.193</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>10.21</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>10.225</v>
+        <v>10.245</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>10.225</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>10.188</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>10.192</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>10.287</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>10.2</v>
+        <v>10.353</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>10.218</v>
+        <v>10.243</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>10.188</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>10.212</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>10.196</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>10.21</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.224</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>10.21</v>
+        <v>10.331</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>10.203</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>10.21</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>10.191</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>10.208</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>10.221</v>
+        <v>10.222</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="F224" s="4" t="n">
-        <v>10.202</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>10.199</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>10.194</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>10.216</v>
+        <v>10.249</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>10.202</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>10.236</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>10.209</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>10.204</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>10.199</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>10.294</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>10.072</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>10.207</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>10.196</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>10.174</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>10.283</v>
+        <v>10.248</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>10.183</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>10.204</v>
+        <v>10.222</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>10.22</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>10.185</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>10.236</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>10.202</v>
+        <v>10.217</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F246" s="4" t="n">
-        <v>10.221</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>10.229</v>
+        <v>10.307</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>10.201</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>10.212</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>10.201</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>10.192</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>10.204</v>
+        <v>10.245</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>10.236</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>10.179</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>10.064</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>10.231</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>10.165</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>10.22</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>10.192</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>10.228</v>
+        <v>10.323</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>10.184</v>
+        <v>10.223</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F262" s="4" t="n">
-        <v>10.187</v>
+        <v>10.259</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>10.329</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>10.226</v>
+        <v>10.063</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>10.225</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="F266" s="4" t="n">
-        <v>10.22</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>10.27</v>
+        <v>10.298</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>10.34</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>10.21</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>10.207</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>10.231</v>
+        <v>10.207</v>
       </c>
     </row>
   </sheetData>

--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>10.236s</t>
+          <t>10.292s</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>10.779</v>
+        <v>11.067</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.201</v>
+        <v>10.289</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.199</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.21</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.24</v>
+        <v>10.302</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.231</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.223</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.244</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.455</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.226</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.247</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.214</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.237</v>
+        <v>10.282</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.263</v>
+        <v>10.282</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.244</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.25</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.21</v>
+        <v>10.273</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.24</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.236</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.23</v>
+        <v>10.477</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.204</v>
+        <v>10.386</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.209</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.22</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.237</v>
+        <v>10.303</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.218</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.207</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.19</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.242</v>
+        <v>10.321</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.22</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.204</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.232</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.254</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.236</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.228</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.208</v>
+        <v>10.288</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.239</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.223</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.319</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.273</v>
+        <v>10.299</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.242</v>
+        <v>10.305</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.212</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.215</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.225</v>
+        <v>10.336</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.241</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>10.22</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>10.218</v>
+        <v>10.309</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10.224</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.265</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.202</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.231</v>
+        <v>10.291</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.236</v>
+        <v>10.462</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.217</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.235</v>
+        <v>10.243</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.206</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.22</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.239</v>
+        <v>10.241</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.249</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.247</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>10.207</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.192</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.246</v>
+        <v>10.266</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.246</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.251</v>
+        <v>10.353</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.245</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.208</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10.21</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.308</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.231</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>10.214</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.21</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.211</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.258</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.239</v>
+        <v>10.261</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.245</v>
+        <v>10.272</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.256</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10.24</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.223</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>10.23</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.225</v>
+        <v>10.285</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.222</v>
+        <v>10.443</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.24</v>
+        <v>10.298</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.221</v>
+        <v>10.272</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.22</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.187</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>10.241</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.254</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.255</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>10.218</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>10.296</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.234</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>10.238</v>
+        <v>10.286</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.254</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.246</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>10.242</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.254</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>10.31</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>10.252</v>
+        <v>10.266</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.206</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>10.22</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>10.226</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>10.251</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10.242</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>10.231</v>
+        <v>10.243</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10.206</v>
+        <v>10.264</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.226</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>10.244</v>
+        <v>10.415</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10.218</v>
+        <v>10.364</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>10.247</v>
+        <v>10.309</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>10.23</v>
+        <v>10.436</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>10.211</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.193</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>10.239</v>
+        <v>10.285</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>10.231</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10.209</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>10.257</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>10.241</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>10.253</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>10.354</v>
+        <v>10.266</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.255</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>10.244</v>
+        <v>10.544</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>10.205</v>
+        <v>10.456</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>10.23</v>
+        <v>10.247</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>10.252</v>
+        <v>10.328</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10.275</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>10.256</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>10.216</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>10.231</v>
+        <v>10.457</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>10.254</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>10.223</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>10.313</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>10.258</v>
+        <v>10.299</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>10.211</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>10.244</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>10.242</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>10.209</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>10.23</v>
+        <v>10.248</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.21</v>
+        <v>10.251</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>10.221</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>10.215</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>10.219</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>10.215</v>
+        <v>10.321</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>10.232</v>
+        <v>10.344</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>10.238</v>
+        <v>10.286</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>10.236</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>10.242</v>
+        <v>10.288</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>10.252</v>
+        <v>10.298</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>10.202</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>10.237</v>
+        <v>10.286</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>10.198</v>
+        <v>10.417</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>10.249</v>
+        <v>10.414</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>10.212</v>
+        <v>10.415</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>10.227</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>10.366</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>10.235</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>10.236</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>10.223</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>10.241</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>10.227</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>10.21</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>10.34</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>10.202</v>
+        <v>10.282</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>10.207</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>10.223</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>10.223</v>
+        <v>10.335</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>10.216</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>10.211</v>
+        <v>10.266</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>10.251</v>
+        <v>10.307</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>10.247</v>
+        <v>10.312</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>10.208</v>
+        <v>10.364</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>10.218</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>10.219</v>
+        <v>10.245</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>10.259</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>10.213</v>
+        <v>10.249</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>10.208</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>10.215</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>10.208</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>10.24</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>10.189</v>
+        <v>10.305</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>10.241</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>10.248</v>
+        <v>10.398</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>10.087</v>
+        <v>10.261</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>10.25</v>
+        <v>10.233</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>10.197</v>
+        <v>10.263</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>10.216</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>10.24</v>
+        <v>10.289</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>10.235</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>10.244</v>
+        <v>10.243</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>10.225</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>10.247</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>10.225</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>10.214</v>
+        <v>10.297</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>10.218</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>10.199</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>10.244</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>10.229</v>
+        <v>10.238</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>10.249</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>10.294</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>10.256</v>
+        <v>10.288</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>10.206</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>10.238</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>10.22</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>10.215</v>
+        <v>10.244</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>10.251</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>10.25</v>
+        <v>10.238</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>10.245</v>
+        <v>10.285</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>10.246</v>
+        <v>10.264</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>10.209</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>10.24</v>
+        <v>10.094</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>10.214</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>10.353</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>10.243</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>10.237</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>10.236</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>10.224</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>10.219</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.232</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>10.331</v>
+        <v>10.375</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>10.231</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>10.235</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>10.209</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>10.247</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>10.222</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="F224" s="4" t="n">
-        <v>10.205</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>10.206</v>
+        <v>10.266</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>10.237</v>
+        <v>10.259</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>10.249</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>10.228</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>10.226</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>10.232</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>10.218</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="F232" s="4" t="n">
-        <v>10.206</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>10.202</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>10.191</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>10.19</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>10.2</v>
+        <v>10.439</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>10.231</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>10.244</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>10.248</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>10.311</v>
+        <v>10.273</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>10.222</v>
+        <v>10.272</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>10.231</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>10.196</v>
+        <v>10.259</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>10.23</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>10.217</v>
+        <v>10.263</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F246" s="4" t="n">
-        <v>10.209</v>
+        <v>10.333</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>10.307</v>
+        <v>10.313</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>10.241</v>
+        <v>10.295</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>10.253</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>10.233</v>
+        <v>10.327</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>10.246</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>10.245</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>10.227</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>10.212</v>
+        <v>10.257</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>10.211</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>10.216</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>10.216</v>
+        <v>10.263</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>10.244</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>10.24</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>10.323</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>10.223</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F262" s="4" t="n">
-        <v>10.259</v>
+        <v>10.295</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>10.232</v>
+        <v>10.384</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>10.063</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>10.216</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="F266" s="4" t="n">
-        <v>10.242</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>10.298</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>10.209</v>
+        <v>10.377</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>10.34</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>10.209</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>10.207</v>
+        <v>10.272</v>
       </c>
     </row>
   </sheetData>

--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>10.292s</t>
+          <t>10.204s</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>11.067</v>
+        <v>11.496</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.289</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.251</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.257</v>
+        <v>10.144</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.302</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.281</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.29</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.271</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.275</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.292</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.306</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.265</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.282</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.282</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.311</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.274</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.273</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.239</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.304</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.477</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.386</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.287</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.29</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.303</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.304</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.292</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.271</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.321</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.284</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.45</v>
+        <v>10.534</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.301</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.287</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.275</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.283</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.288</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.28</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.283</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.324</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.299</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.305</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.293</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.324</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.336</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.306</v>
+        <v>10.204</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>10.294</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>10.309</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10.277</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.253</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.37</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.291</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.462</v>
+        <v>10.359</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.31</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.243</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.246</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.26</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.241</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.242</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.267</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>10.293</v>
+        <v>10.349</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.252</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.266</v>
+        <v>10.147</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.247</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.353</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.254</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.296</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10.31</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.232</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.279</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>10.256</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.3</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.292</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.275</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.261</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.272</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.281</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10.294</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.267</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>10.346</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.285</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.443</v>
+        <v>10.367</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.298</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.272</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.274</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.296</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>10.267</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.281</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.254</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>10.277</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>10.271</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.292</v>
+        <v>10.211</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>10.286</v>
+        <v>10.226</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.262</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>10.269</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.278</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>10.275</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>10.266</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.252</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>10.253</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>10.329</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>10.287</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10.274</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>10.243</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10.264</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.255</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>10.415</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10.364</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>10.309</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>10.436</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>10.24</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.279</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>10.285</v>
+        <v>10.151</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>10.306</v>
+        <v>10.154</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10.269</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>10.253</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>10.306</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>10.244</v>
+        <v>10.353</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>10.266</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.27</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>10.544</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>10.456</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>10.247</v>
+        <v>10.232</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>10.328</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10.258</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>10.252</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>10.253</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>10.457</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>10.304</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>10.315</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>10.246</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>10.299</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>10.292</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>10.255</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>10.28</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>10.315</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>10.248</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.251</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>10.258</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>10.29</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>10.252</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>10.321</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>10.344</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>10.286</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>10.231</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>10.288</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>10.298</v>
+        <v>10.516</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>10.315</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>10.286</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>10.417</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>10.414</v>
+        <v>10.359</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>10.415</v>
+        <v>10.417</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>10.276</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>10.26</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>10.262</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>10.271</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>10.269</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>10.283</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>10.31</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>10.296</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>10.317</v>
+        <v>10.076</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>10.282</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>10.265</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>10.325</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>10.335</v>
+        <v>10.085</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>10.311</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>10.266</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>10.307</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>10.312</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>10.364</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>10.293</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>10.245</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>10.267</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>10.249</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>10.281</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>10.237</v>
+        <v>10.351</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>10.279</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>10.296</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>10.305</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>10.277</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>10.398</v>
+        <v>10.382</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>10.261</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>10.233</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>10.263</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>10.318</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>10.289</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>10.275</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>10.243</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>10.257</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>10.257</v>
+        <v>10.145</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>10.287</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>10.297</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>10.265</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>10.318</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>10.292</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>10.238</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>10.252</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>10.265</v>
+        <v>10.154</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>10.288</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>10.239</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>10.284</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>10.23</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>10.244</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>10.267</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>10.238</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>10.285</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>10.264</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>10.301</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>10.094</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>10.39</v>
+        <v>10.327</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>10.281</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>10.301</v>
+        <v>10.213</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>10.271</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>10.276</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>10.276</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>10.274</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.25</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>10.375</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>10.252</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>10.255</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>10.283</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>10.262</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>10.274</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="F224" s="4" t="n">
-        <v>10.255</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>10.266</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>10.259</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>10.294</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>10.246</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>10.271</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>10.26</v>
+        <v>10.248</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>10.242</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="F232" s="4" t="n">
-        <v>10.274</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>10.267</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>10.257</v>
+        <v>10.448</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>10.262</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>10.439</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>10.265</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>10.275</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>10.39</v>
+        <v>10.342</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>10.273</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>10.272</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>10.26</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>10.259</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>10.27</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>10.263</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F246" s="4" t="n">
-        <v>10.333</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>10.313</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>10.295</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>10.239</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>10.327</v>
+        <v>10.198</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>10.281</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>10.254</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>10.292</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>10.257</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>10.276</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>10.26</v>
+        <v>10.199</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>10.263</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>10.228</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>10.283</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>10.31</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>10.269</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F262" s="4" t="n">
-        <v>10.295</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>10.384</v>
+        <v>10.342</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>10.274</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>10.35</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="F266" s="4" t="n">
-        <v>10.267</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>10.236</v>
+        <v>10.208</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>10.377</v>
+        <v>10.342</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>10.26</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>10.265</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>10.272</v>
+        <v>10.203</v>
       </c>
     </row>
   </sheetData>

--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>10.204s</t>
+          <t>10.397s</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>11.496</v>
+        <v>11.081</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.226</v>
+        <v>10.259</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.204</v>
+        <v>10.395</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.144</v>
+        <v>10.132</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.218</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.181</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.178</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.189</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.206</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.169</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.193</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.186</v>
+        <v>12.354</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.153</v>
+        <v>10.282</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.198</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.179</v>
+        <v>10.289</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.178</v>
+        <v>10.307</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.168</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.185</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.166</v>
+        <v>10.601</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.177</v>
+        <v>10.333</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.192</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.166</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.179</v>
+        <v>10.288</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.171</v>
+        <v>10.316</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.189</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.191</v>
+        <v>10.297</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.182</v>
+        <v>10.395</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.182</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.153</v>
+        <v>10.597</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.534</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.198</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.172</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.21</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.181</v>
+        <v>10.303</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.159</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.178</v>
+        <v>10.297</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.161</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.202</v>
+        <v>11.137</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.179</v>
+        <v>10.291</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.175</v>
+        <v>10.298</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.176</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.191</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.171</v>
+        <v>10.336</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.204</v>
+        <v>10.345</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>10.184</v>
+        <v>11.125</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>10.193</v>
+        <v>10.362</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10.157</v>
+        <v>10.308</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.195</v>
+        <v>10.253</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.171</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.189</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.359</v>
+        <v>10.452</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.186</v>
+        <v>10.893</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.165</v>
+        <v>12.174</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.194</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.175</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.159</v>
+        <v>10.504</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.174</v>
+        <v>10.472</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.183</v>
+        <v>10.382</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>10.349</v>
+        <v>10.291</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.196</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.147</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.192</v>
+        <v>10.303</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.2</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.179</v>
+        <v>10.265</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.186</v>
+        <v>10.302</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10.166</v>
+        <v>10.347</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.188</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.199</v>
+        <v>10.273</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>10.158</v>
+        <v>10.322</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.171</v>
+        <v>10.459</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.185</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.211</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.177</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.203</v>
+        <v>10.314</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.202</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10.199</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.164</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>10.203</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.158</v>
+        <v>10.489</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.367</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.188</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.164</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.197</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.184</v>
+        <v>10.334</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>10.194</v>
+        <v>10.321</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.2</v>
+        <v>10.402</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.21</v>
+        <v>10.391</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>10.329</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>10.178</v>
+        <v>10.323</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.211</v>
+        <v>10.291</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>10.226</v>
+        <v>10.351</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.173</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.2</v>
+        <v>10.299</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>10.197</v>
+        <v>10.312</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.215</v>
+        <v>10.393</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>10.197</v>
+        <v>10.323</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>10.21</v>
+        <v>10.289</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.19</v>
+        <v>10.273</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>10.176</v>
+        <v>10.306</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>10.187</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>10.202</v>
+        <v>10.282</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10.188</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>10.166</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10.201</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.187</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>10.166</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10.188</v>
+        <v>10.328</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>10.178</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>10.319</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>10.188</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.157</v>
+        <v>10.356</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>10.151</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>10.154</v>
+        <v>10.291</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10.158</v>
+        <v>10.432</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>10.187</v>
+        <v>10.454</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>10.189</v>
+        <v>10.271</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>10.353</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>10.205</v>
+        <v>10.363</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.205</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>10.165</v>
+        <v>10.286</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>10.36</v>
+        <v>10.655</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>10.232</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>10.2</v>
+        <v>10.302</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10.219</v>
+        <v>10.333</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>10.19</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>10.218</v>
+        <v>10.303</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>10.184</v>
+        <v>10.273</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>10.178</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>10.174</v>
+        <v>10.321</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>10.186</v>
+        <v>10.291</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>10.2</v>
+        <v>10.343</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>10.216</v>
+        <v>10.327</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>10.19</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>10.182</v>
+        <v>10.312</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>10.197</v>
+        <v>10.316</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>10.197</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.17</v>
+        <v>10.285</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>10.173</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>10.214</v>
+        <v>10.308</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>10.167</v>
+        <v>10.909</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>10.182</v>
+        <v>10.328</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>10.18</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>10.189</v>
+        <v>10.372</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>10.192</v>
+        <v>10.347</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>10.179</v>
+        <v>10.345</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>10.516</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>10.157</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>10.201</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>10.196</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>10.359</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>10.417</v>
+        <v>10.492</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>10.205</v>
+        <v>10.409</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>10.196</v>
+        <v>10.272</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>10.177</v>
+        <v>10.333</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>10.195</v>
+        <v>10.323</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>10.192</v>
+        <v>10.322</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>10.21</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>10.175</v>
+        <v>10.348</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>10.185</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>10.076</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>10.193</v>
+        <v>10.323</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>10.2</v>
+        <v>10.288</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>10.157</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>10.085</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>10.159</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>10.215</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>10.202</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>10.206</v>
+        <v>10.351</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>10.16</v>
+        <v>10.338</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>10.167</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>10.184</v>
+        <v>10.445</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>10.179</v>
+        <v>10.762</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>10.181</v>
+        <v>10.326</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>10.201</v>
+        <v>10.328</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>10.351</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>10.196</v>
+        <v>10.822</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>10.209</v>
+        <v>10.331</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>10.186</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>10.181</v>
+        <v>10.316</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>10.382</v>
+        <v>10.439</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>10.212</v>
+        <v>10.473</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>10.205</v>
+        <v>10.419</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>10.176</v>
+        <v>10.298</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>10.22</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>10.198</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>10.202</v>
+        <v>10.313</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>10.165</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>10.199</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>10.145</v>
+        <v>10.358</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>10.192</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>10.21</v>
+        <v>10.349</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>10.194</v>
+        <v>10.498</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>10.19</v>
+        <v>10.294</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>10.18</v>
+        <v>10.328</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>10.205</v>
+        <v>10.377</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>10.179</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>10.154</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>10.208</v>
+        <v>10.369</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>10.168</v>
+        <v>10.432</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>10.163</v>
+        <v>10.473</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>10.188</v>
+        <v>10.307</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>10.22</v>
+        <v>11.951</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>10.183</v>
+        <v>10.305</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>10.317</v>
+        <v>10.436</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>10.159</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>10.169</v>
+        <v>10.339</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>10.187</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>10.206</v>
+        <v>10.478</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>10.327</v>
+        <v>10.389</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>10.198</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>10.213</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>10.199</v>
+        <v>10.373</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>10.237</v>
+        <v>10.368</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>10.158</v>
+        <v>10.297</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>10.186</v>
+        <v>10.367</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.155</v>
+        <v>10.327</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>10.163</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>10.192</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>10.188</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>10.164</v>
+        <v>10.334</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>10.196</v>
+        <v>10.351</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>10.19</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="F224" s="4" t="n">
-        <v>10.172</v>
+        <v>10.374</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>10.171</v>
+        <v>10.382</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>10.18</v>
+        <v>10.267</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>10.203</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>10.177</v>
+        <v>10.471</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>10.193</v>
+        <v>10.326</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>10.248</v>
+        <v>10.354</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>10.19</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="F232" s="4" t="n">
-        <v>10.202</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>10.194</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>10.448</v>
+        <v>10.337</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>10.195</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>10.188</v>
+        <v>10.298</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>10.183</v>
+        <v>10.466</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>10.178</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>10.342</v>
+        <v>10.404</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>10.208</v>
+        <v>12.587</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>10.304</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>10.184</v>
+        <v>10.295</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>10.195</v>
+        <v>10.246</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>10.199</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>10.177</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F246" s="4" t="n">
-        <v>10.197</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>10.188</v>
+        <v>10.327</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>10.198</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>10.198</v>
+        <v>13.768</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>10.198</v>
+        <v>10.337</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>10.173</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>10.162</v>
+        <v>10.342</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>10.159</v>
+        <v>10.412</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>10.195</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>10.186</v>
+        <v>10.321</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>10.199</v>
+        <v>10.725</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>10.177</v>
+        <v>10.337</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>10.178</v>
+        <v>10.347</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>10.176</v>
+        <v>11.861</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>10.168</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>10.201</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F262" s="4" t="n">
-        <v>10.18</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>10.342</v>
+        <v>10.375</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>10.182</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>10.189</v>
+        <v>10.461</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="F266" s="4" t="n">
-        <v>10.192</v>
+        <v>10.316</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>10.208</v>
+        <v>10.343</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>10.342</v>
+        <v>10.538</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>10.183</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>10.181</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>10.203</v>
+        <v>10.308</v>
       </c>
     </row>
   </sheetData>

--- a/test-reports/web_selenium_e2e_report.xlsx
+++ b/test-reports/web_selenium_e2e_report.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>10.397s</t>
+          <t>10.189s</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>11.081</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.259</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.395</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.132</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.35</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.37</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.341</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.318</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.277</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.294</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.317</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12.354</v>
+        <v>10.147</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.282</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.292</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.289</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.307</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.3</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.276</v>
+        <v>10.201</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.601</v>
+        <v>10.207</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.333</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.287</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.318</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.288</v>
+        <v>10.156</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.316</v>
+        <v>10.156</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.332</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.297</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.395</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.26</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.597</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.49</v>
+        <v>10.494</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.274</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.32</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.277</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.303</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>10.269</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.297</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.279</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>11.137</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.291</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.298</v>
+        <v>10.149</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.265</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.269</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.336</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.345</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>11.125</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>10.362</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>10.308</v>
+        <v>10.228</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.253</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.324</v>
+        <v>10.148</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.281</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10.452</v>
+        <v>10.331</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.893</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>12.174</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.265</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.26</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.504</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.472</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.382</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>10.291</v>
+        <v>10.453</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.301</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.346</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.303</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.311</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.265</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.302</v>
+        <v>10.187</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>10.347</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.341</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.273</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>10.322</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.459</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.332</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.3</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.304</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.314</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.346</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>10.35</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.306</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>10.311</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.489</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.324</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.304</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.319</v>
+        <v>10.202</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.33</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.334</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>10.321</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.402</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.391</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>10.31</v>
+        <v>10.383</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>10.323</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.291</v>
+        <v>10.152</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>10.351</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.276</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.299</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>10.312</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.393</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>10.323</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>10.289</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.273</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>10.306</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>10.271</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>10.282</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10.33</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>10.281</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10.33</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>10.29</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>10.315</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10.328</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>10.51</v>
+        <v>10.183</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>10.346</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>10.315</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.356</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>10.277</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>10.291</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10.432</v>
+        <v>10.156</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>10.454</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>10.271</v>
+        <v>10.209</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>10.29</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>10.363</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.255</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>10.286</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>10.655</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>10.329</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>10.302</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10.333</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>10.276</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>10.303</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>10.273</v>
+        <v>10.214</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>10.3</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>10.321</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>10.291</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>10.343</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>10.327</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>10.325</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>10.312</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>10.316</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>10.279</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.285</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>10.346</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>10.308</v>
+        <v>10.182</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>10.909</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>10.328</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>10.33</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>10.372</v>
+        <v>10.151</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>10.347</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>10.345</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>10.278</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>10.276</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>10.283</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>10.283</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>10.45</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>10.492</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>10.409</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>10.272</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>10.333</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>10.323</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>10.322</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>10.279</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>10.348</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>10.301</v>
+        <v>10.071</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>10.296</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>10.323</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>10.288</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>10.283</v>
+        <v>10.378</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>10.301</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>10.32</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>10.325</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>10.319</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>10.351</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>10.338</v>
+        <v>10.154</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>10.301</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>10.445</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>10.762</v>
+        <v>10.231</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>10.326</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>10.328</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>10.301</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>10.822</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>10.331</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>10.318</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>10.316</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>10.439</v>
+        <v>10.326</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>10.473</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>10.419</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>10.298</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>10.304</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>10.284</v>
+        <v>10.181</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>10.313</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>10.293</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>10.317</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>10.358</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>10.33</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>10.349</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>10.498</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>10.294</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>10.328</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>10.377</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>10.311</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>10.293</v>
+        <v>10.151</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>10.369</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>10.432</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>10.473</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>10.307</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>11.951</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>10.305</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>10.436</v>
+        <v>10.156</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>10.315</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>10.339</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>10.292</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>10.478</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>10.389</v>
+        <v>10.325</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>10.341</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>10.168</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>10.373</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>10.368</v>
+        <v>10.178</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>10.297</v>
+        <v>10.148</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>10.367</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.327</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>10.11</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>10.317</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>10.31</v>
+        <v>10.184</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>10.334</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>10.351</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>10.292</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="F224" s="4" t="n">
-        <v>10.374</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>10.382</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>10.267</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>10.301</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>10.471</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>10.326</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>10.354</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>10.332</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="F232" s="4" t="n">
-        <v>10.29</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>10.296</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>10.337</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>10.283</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>10.298</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>10.466</v>
+        <v>10.167</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>10.35</v>
+        <v>10.158</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>10.404</v>
+        <v>10.354</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>12.587</v>
+        <v>10.173</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>10.24</v>
+        <v>10.159</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>10.295</v>
+        <v>10.153</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>10.246</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>10.3</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>10.33</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F246" s="4" t="n">
-        <v>10.304</v>
+        <v>10.186</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>10.327</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>10.315</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>13.768</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>10.337</v>
+        <v>10.163</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>10.325</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>10.342</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>10.412</v>
+        <v>10.177</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>10.3</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>10.321</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>10.725</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>10.337</v>
+        <v>10.175</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>10.347</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>11.861</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>10.33</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>10.319</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F262" s="4" t="n">
-        <v>10.32</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>10.375</v>
+        <v>10.171</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>10.36</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>10.461</v>
+        <v>10.165</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="F266" s="4" t="n">
-        <v>10.316</v>
+        <v>10.169</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>10.343</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>10.538</v>
+        <v>10.283</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>10.346</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>10.296</v>
+        <v>10.172</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>10.308</v>
+        <v>10.171</v>
       </c>
     </row>
   </sheetData>
